--- a/연구코드/aec/results/신촌/multivariable_results.xlsx
+++ b/연구코드/aec/results/신촌/multivariable_results.xlsx
@@ -712,13 +712,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6146</v>
+        <v>0.6151</v>
       </c>
       <c r="C14" t="n">
-        <v>0.655</v>
+        <v>0.6567</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7221</v>
+        <v>0.723</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -733,13 +733,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5783</v>
+        <v>0.5769</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6211</v>
+        <v>0.6214</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6881</v>
+        <v>0.6916</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -754,13 +754,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6522</v>
+        <v>0.653</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6911</v>
+        <v>0.6949</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7531</v>
+        <v>0.7542</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>8.9108</v>
       </c>
       <c r="C2" t="n">
-        <v>7411.3487</v>
+        <v>7411.3489</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
@@ -2868,7 +2868,7 @@
         <v>105.3565</v>
       </c>
       <c r="C21" t="n">
-        <v>5.698362895386974e+45</v>
+        <v>5.698367857291181e+45</v>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
@@ -3154,7 +3154,7 @@
         <v>117.6051</v>
       </c>
       <c r="C34" t="n">
-        <v>1.189168026865881e+51</v>
+        <v>1.189169163028276e+51</v>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
@@ -3418,7 +3418,7 @@
         <v>113.8601</v>
       </c>
       <c r="C46" t="n">
-        <v>2.810777264241634e+49</v>
+        <v>2.810780034252235e+49</v>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
@@ -3528,7 +3528,7 @@
         <v>100.0617</v>
       </c>
       <c r="C51" t="n">
-        <v>2.859289574977098e+43</v>
+        <v>2.859291974418416e+43</v>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
@@ -3550,7 +3550,7 @@
         <v>84.91030000000001</v>
       </c>
       <c r="C52" t="n">
-        <v>7.517643574938535e+36</v>
+        <v>7.517649154081424e+36</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
@@ -3594,7 +3594,7 @@
         <v>176.5196</v>
       </c>
       <c r="C54" t="n">
-        <v>4.586562914514311e+76</v>
+        <v>4.586569879261268e+76</v>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
@@ -3777,7 +3777,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7221</v>
+        <v>0.723</v>
       </c>
     </row>
     <row r="5">
@@ -3787,7 +3787,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6881</v>
+        <v>0.6916</v>
       </c>
     </row>
     <row r="6">
@@ -3797,7 +3797,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7531</v>
+        <v>0.7542</v>
       </c>
     </row>
     <row r="7">
@@ -4333,7 +4333,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6146</v>
+        <v>0.6151</v>
       </c>
     </row>
     <row r="5">
@@ -4343,7 +4343,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5783</v>
+        <v>0.5769</v>
       </c>
     </row>
     <row r="6">
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6522</v>
+        <v>0.653</v>
       </c>
     </row>
     <row r="7">
@@ -5174,7 +5174,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.655</v>
+        <v>0.6567</v>
       </c>
     </row>
     <row r="5">
@@ -5184,7 +5184,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6211</v>
+        <v>0.6214</v>
       </c>
     </row>
     <row r="6">
@@ -5194,7 +5194,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6911</v>
+        <v>0.6949</v>
       </c>
     </row>
     <row r="7">

--- a/연구코드/aec/results/신촌/multivariable_results.xlsx
+++ b/연구코드/aec/results/신촌/multivariable_results.xlsx
@@ -519,16 +519,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0741</v>
+        <v>0.074</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5145999999999999</v>
+        <v>0.5203</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5437</v>
+        <v>0.548</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5879</v>
+        <v>0.5901</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -543,16 +543,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0704</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5139</v>
+        <v>0.5195</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5411</v>
+        <v>0.5459000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5699</v>
+        <v>0.5726</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -568,22 +568,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.9629e-19</t>
+          <t>3.8498e-20</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.9390e-199</t>
+          <t>1.1463e-202</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>9.8029e-210</t>
+          <t>1.4817e-213</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3.6868e-195</t>
+          <t>2.5855e-197</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -599,16 +599,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>29.7692</v>
+        <v>29.6475</v>
       </c>
       <c r="C7" t="n">
-        <v>21.5534</v>
+        <v>21.3386</v>
       </c>
       <c r="D7" t="n">
-        <v>20.8984</v>
+        <v>20.7131</v>
       </c>
       <c r="E7" t="n">
-        <v>19.8599</v>
+        <v>19.7243</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -623,16 +623,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24.0924</v>
+        <v>24.0766</v>
       </c>
       <c r="C8" t="n">
-        <v>15.9728</v>
+        <v>15.9332</v>
       </c>
       <c r="D8" t="n">
-        <v>15.5163</v>
+        <v>15.4866</v>
       </c>
       <c r="E8" t="n">
-        <v>14.6475</v>
+        <v>14.5889</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -647,16 +647,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12225.91</v>
+        <v>12213.51</v>
       </c>
       <c r="C9" t="n">
-        <v>11400.28</v>
+        <v>11374.86</v>
       </c>
       <c r="D9" t="n">
-        <v>11331.95</v>
+        <v>11307.35</v>
       </c>
       <c r="E9" t="n">
-        <v>11294.59</v>
+        <v>11275.2</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -671,16 +671,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12256.78</v>
+        <v>12239.24</v>
       </c>
       <c r="C10" t="n">
-        <v>11415.72</v>
+        <v>11390.3</v>
       </c>
       <c r="D10" t="n">
-        <v>11373.12</v>
+        <v>11343.37</v>
       </c>
       <c r="E10" t="n">
-        <v>11572.48</v>
+        <v>11547.94</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -755,16 +755,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.609</v>
+        <v>0.6117</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6105</v>
+        <v>0.6097</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6506</v>
+        <v>0.6497000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7285</v>
+        <v>0.7282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -779,16 +779,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.575</v>
+        <v>0.5770999999999999</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5748</v>
+        <v>0.5684</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6139</v>
+        <v>0.615</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6975</v>
+        <v>0.6986</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -803,16 +803,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6429</v>
+        <v>0.647</v>
       </c>
       <c r="C16" t="n">
-        <v>0.651</v>
+        <v>0.6476</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6858</v>
+        <v>0.6865</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7592</v>
+        <v>0.7591</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1.5686e-01</t>
+          <t>3.2965e-01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -838,12 +838,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.7321e-01</t>
+          <t>1.6756e-01</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>4.4624e-01</t>
+          <t>1.8895e-01</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -887,16 +887,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.0394</v>
+        <v>0.0369</v>
       </c>
       <c r="C19" t="n">
         <v>0.0286</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0741</v>
+        <v>0.0727</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1811</v>
+        <v>0.1791</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -911,16 +911,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.1826</v>
+        <v>0.1825</v>
       </c>
       <c r="C20" t="n">
         <v>0.1829</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1769</v>
+        <v>0.1767</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1625</v>
+        <v>0.1623</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -935,16 +935,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1404.41</v>
+        <v>1404.66</v>
       </c>
       <c r="C21" t="n">
         <v>1407.95</v>
       </c>
       <c r="D21" t="n">
-        <v>1377.54</v>
+        <v>1376.83</v>
       </c>
       <c r="E21" t="n">
-        <v>1369.13</v>
+        <v>1369.12</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -959,16 +959,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1435.28</v>
+        <v>1430.39</v>
       </c>
       <c r="C22" t="n">
         <v>1423.39</v>
       </c>
       <c r="D22" t="n">
-        <v>1418.71</v>
+        <v>1412.86</v>
       </c>
       <c r="E22" t="n">
-        <v>1647.01</v>
+        <v>1641.86</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>104.61</v>
+        <v>104.6983</v>
       </c>
       <c r="C2" t="n">
-        <v>102.951</v>
+        <v>103.0574</v>
       </c>
       <c r="D2" t="n">
-        <v>106.2691</v>
+        <v>106.3392</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8457</v>
+        <v>0.8364</v>
       </c>
       <c r="F2" t="n">
-        <v>123.703</v>
+        <v>125.1764</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -1061,23 +1061,23 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>43.028</v>
+        <v>42.9307</v>
       </c>
       <c r="C3" t="n">
-        <v>40.6546</v>
+        <v>40.5869</v>
       </c>
       <c r="D3" t="n">
-        <v>45.4014</v>
+        <v>45.2744</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2098</v>
+        <v>1.1946</v>
       </c>
       <c r="F3" t="n">
-        <v>35.5665</v>
+        <v>35.9358</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.8640e-192</t>
+          <t>2.3833e-195</t>
         </is>
       </c>
     </row>
@@ -1088,50 +1088,50 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-4.4216</v>
+        <v>-4.3971</v>
       </c>
       <c r="C4" t="n">
-        <v>-5.6049</v>
+        <v>-5.5692</v>
       </c>
       <c r="D4" t="n">
-        <v>-3.2382</v>
+        <v>-3.225</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6032</v>
+        <v>0.5975</v>
       </c>
       <c r="F4" t="n">
-        <v>-7.3304</v>
+        <v>-7.3596</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>4.0875e-13</t>
+          <t>3.3132e-13</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>p25_z</t>
+          <t>mean_z</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-8.804</v>
+        <v>4.862</v>
       </c>
       <c r="C5" t="n">
-        <v>-18.2319</v>
+        <v>3.6516</v>
       </c>
       <c r="D5" t="n">
-        <v>0.624</v>
+        <v>6.0724</v>
       </c>
       <c r="E5" t="n">
-        <v>4.8057</v>
+        <v>0.617</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.832</v>
+        <v>7.8803</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>6.7187e-02</t>
+          <t>7.0078e-15</t>
         </is>
       </c>
     </row>
@@ -1142,23 +1142,23 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-2.7961</v>
+        <v>-1.5547</v>
       </c>
       <c r="C6" t="n">
-        <v>-4.6642</v>
+        <v>-2.8449</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.928</v>
+        <v>-0.2644</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9522</v>
+        <v>0.6577</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.9364</v>
+        <v>-2.364</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.3805e-03</t>
+          <t>1.8232e-02</t>
         </is>
       </c>
     </row>
@@ -1169,23 +1169,23 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.4363</v>
+        <v>1.8922</v>
       </c>
       <c r="C7" t="n">
-        <v>0.089</v>
+        <v>0.6369</v>
       </c>
       <c r="D7" t="n">
-        <v>2.7836</v>
+        <v>3.1474</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6868</v>
+        <v>0.6398</v>
       </c>
       <c r="F7" t="n">
-        <v>2.0914</v>
+        <v>2.9573</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.6693e-02</t>
+          <t>3.1608e-03</t>
         </is>
       </c>
     </row>
@@ -1196,50 +1196,23 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8082</v>
+        <v>0.9151</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.4076</v>
+        <v>-0.2832</v>
       </c>
       <c r="D8" t="n">
-        <v>2.0241</v>
+        <v>2.1133</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6197</v>
+        <v>0.6108</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3041</v>
+        <v>1.4982</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.9244e-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>mean_z</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>13.2929</v>
-      </c>
-      <c r="C9" t="n">
-        <v>4.2211</v>
-      </c>
-      <c r="D9" t="n">
-        <v>22.3647</v>
-      </c>
-      <c r="E9" t="n">
-        <v>4.6241</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2.8747</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>4.1122e-03</t>
+          <t>1.3433e-01</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1306,26 +1279,26 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-1.2251</v>
+        <v>-1.2337</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2937</v>
+        <v>0.2912</v>
       </c>
       <c r="D2" t="n">
-        <v>0.242</v>
+        <v>0.24</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3566</v>
+        <v>0.3534</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0989</v>
+        <v>0.0988</v>
       </c>
       <c r="G2" t="n">
-        <v>-12.3883</v>
+        <v>-12.4921</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3.0256e-35</t>
+          <t>8.2464e-36</t>
         </is>
       </c>
     </row>
@@ -1336,26 +1309,26 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.099</v>
+        <v>0.1159</v>
       </c>
       <c r="C3" t="n">
-        <v>1.104</v>
+        <v>1.1229</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8428</v>
+        <v>0.8586</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4463</v>
+        <v>1.4686</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1378</v>
+        <v>0.1369</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7184</v>
+        <v>0.8464</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4.7252e-01</t>
+          <t>3.9733e-01</t>
         </is>
       </c>
     </row>
@@ -1366,56 +1339,56 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3885</v>
+        <v>0.3916</v>
       </c>
       <c r="C4" t="n">
-        <v>1.4748</v>
+        <v>1.4793</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2753</v>
+        <v>1.2795</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7054</v>
+        <v>1.7103</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0742</v>
+        <v>0.074</v>
       </c>
       <c r="G4" t="n">
-        <v>5.2391</v>
+        <v>5.2898</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.6138e-07</t>
+          <t>1.2246e-07</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>p25_z</t>
+          <t>mean_z</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7057</v>
+        <v>-0.3925</v>
       </c>
       <c r="C5" t="n">
-        <v>2.0253</v>
+        <v>0.6754</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5956</v>
+        <v>0.5741000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>6.8871</v>
+        <v>0.7946</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6245000000000001</v>
+        <v>0.0829</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1301</v>
+        <v>-4.7333</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.5842e-01</t>
+          <t>2.2090e-06</t>
         </is>
       </c>
     </row>
@@ -1426,26 +1399,26 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3262</v>
+        <v>0.2363</v>
       </c>
       <c r="C6" t="n">
-        <v>1.3857</v>
+        <v>1.2665</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1196</v>
+        <v>1.092</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7149</v>
+        <v>1.4689</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1088</v>
+        <v>0.0756</v>
       </c>
       <c r="G6" t="n">
-        <v>2.9989</v>
+        <v>3.1241</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.7092e-03</t>
+          <t>1.7836e-03</t>
         </is>
       </c>
     </row>
@@ -1456,26 +1429,26 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.1631</v>
+        <v>-0.1981</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8495</v>
+        <v>0.8203</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7269</v>
+        <v>0.7099</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9928</v>
+        <v>0.9479</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0795</v>
+        <v>0.0738</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.0511</v>
+        <v>-2.6859</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4.0254e-02</t>
+          <t>7.2344e-03</t>
         </is>
       </c>
     </row>
@@ -1486,56 +1459,26 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.0522</v>
+        <v>-0.0624</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9491000000000001</v>
+        <v>0.9395</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7755</v>
+        <v>0.7644</v>
       </c>
       <c r="E8" t="n">
-        <v>1.1617</v>
+        <v>1.1546</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1031</v>
+        <v>0.1052</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5062</v>
+        <v>-0.5935</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6.1271e-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>mean_z</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>-1.0541</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.3485</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.1089</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.1154</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.5935</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-1.7759</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>7.5747e-02</t>
+          <t>5.5285e-01</t>
         </is>
       </c>
     </row>
@@ -1582,7 +1525,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5437</v>
+        <v>0.548</v>
       </c>
     </row>
     <row r="4">
@@ -1592,7 +1535,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5411</v>
+        <v>0.5459000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -1602,7 +1545,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>214.6281</v>
+        <v>255.0083</v>
       </c>
     </row>
     <row r="6">
@@ -1613,7 +1556,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>9.8029e-210</t>
+          <t>1.4817e-213</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1567,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20.8984</v>
+        <v>20.7131</v>
       </c>
     </row>
     <row r="8">
@@ -1634,7 +1577,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15.5163</v>
+        <v>15.4866</v>
       </c>
     </row>
     <row r="9">
@@ -1644,7 +1587,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11331.95</v>
+        <v>11307.35</v>
       </c>
     </row>
     <row r="10">
@@ -1654,7 +1597,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11373.12</v>
+        <v>11343.37</v>
       </c>
     </row>
   </sheetData>
@@ -1710,7 +1653,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6506</v>
+        <v>0.6497000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -1720,7 +1663,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6139</v>
+        <v>0.615</v>
       </c>
     </row>
     <row r="6">
@@ -1730,7 +1673,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6858</v>
+        <v>0.6865</v>
       </c>
     </row>
     <row r="7">
@@ -1740,7 +1683,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11.5345</v>
+        <v>11.6491</v>
       </c>
     </row>
     <row r="8">
@@ -1751,7 +1694,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.7321e-01</t>
+          <t>1.6756e-01</t>
         </is>
       </c>
     </row>
@@ -1774,7 +1717,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0741</v>
+        <v>0.0727</v>
       </c>
     </row>
     <row r="11">
@@ -1784,7 +1727,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1769</v>
+        <v>0.1767</v>
       </c>
     </row>
     <row r="12">
@@ -1794,7 +1737,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1377.54</v>
+        <v>1376.83</v>
       </c>
     </row>
     <row r="13">
@@ -1804,7 +1747,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1418.71</v>
+        <v>1412.86</v>
       </c>
     </row>
     <row r="14">
@@ -1828,7 +1771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1875,23 +1818,23 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>89.2064</v>
+        <v>89.18600000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>49.2807</v>
+        <v>49.5493</v>
       </c>
       <c r="D2" t="n">
-        <v>129.1322</v>
+        <v>128.8228</v>
       </c>
       <c r="E2" t="n">
-        <v>20.3504</v>
+        <v>20.2031</v>
       </c>
       <c r="F2" t="n">
-        <v>4.3835</v>
+        <v>4.4145</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.2686e-05</t>
+          <t>1.1024e-05</t>
         </is>
       </c>
     </row>
@@ -1902,23 +1845,23 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>42.1725</v>
+        <v>42.0194</v>
       </c>
       <c r="C3" t="n">
-        <v>39.8167</v>
+        <v>39.6885</v>
       </c>
       <c r="D3" t="n">
-        <v>44.5283</v>
+        <v>44.3504</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2008</v>
+        <v>1.1881</v>
       </c>
       <c r="F3" t="n">
-        <v>35.1211</v>
+        <v>35.3671</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>4.2857e-187</t>
+          <t>5.3138e-189</t>
         </is>
       </c>
     </row>
@@ -1929,50 +1872,50 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-4.72</v>
+        <v>-4.6932</v>
       </c>
       <c r="C4" t="n">
-        <v>-5.9133</v>
+        <v>-5.8778</v>
       </c>
       <c r="D4" t="n">
-        <v>-3.5266</v>
+        <v>-3.5086</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6083</v>
+        <v>0.6038</v>
       </c>
       <c r="F4" t="n">
-        <v>-7.7599</v>
+        <v>-7.7729</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.7933e-14</t>
+          <t>1.6245e-14</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>p25_z</t>
+          <t>mean_z</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-12.9791</v>
+        <v>6.6717</v>
       </c>
       <c r="C5" t="n">
-        <v>-22.5509</v>
+        <v>5.3405</v>
       </c>
       <c r="D5" t="n">
-        <v>-3.4074</v>
+        <v>8.0029</v>
       </c>
       <c r="E5" t="n">
-        <v>4.8788</v>
+        <v>0.6785</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.6603</v>
+        <v>9.8324</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>7.9092e-03</t>
+          <t>5.2620e-22</t>
         </is>
       </c>
     </row>
@@ -1983,23 +1926,23 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-3.7146</v>
+        <v>-1.8512</v>
       </c>
       <c r="C6" t="n">
-        <v>-5.645</v>
+        <v>-3.1853</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.7842</v>
+        <v>-0.5171</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9839</v>
+        <v>0.68</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.7752</v>
+        <v>-2.7224</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.6757e-04</t>
+          <t>6.5745e-03</t>
         </is>
       </c>
     </row>
@@ -2010,23 +1953,23 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.5075</v>
+        <v>2.0916</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0974</v>
+        <v>0.747</v>
       </c>
       <c r="D7" t="n">
-        <v>2.9176</v>
+        <v>3.4362</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7187</v>
+        <v>0.6854</v>
       </c>
       <c r="F7" t="n">
-        <v>2.0974</v>
+        <v>3.0519</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.6163e-02</t>
+          <t>2.3232e-03</t>
         </is>
       </c>
     </row>
@@ -2037,1292 +1980,1265 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4208</v>
+        <v>0.6138</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.8828</v>
+        <v>-0.673</v>
       </c>
       <c r="D8" t="n">
-        <v>1.7243</v>
+        <v>1.9007</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6644</v>
+        <v>0.6559</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6333</v>
+        <v>0.9359</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>5.2668e-01</t>
+          <t>3.4953e-01</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mean_z</t>
+          <t>kvp_z</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19.2373</v>
+        <v>2.7404</v>
       </c>
       <c r="C9" t="n">
-        <v>9.9232</v>
+        <v>1.275</v>
       </c>
       <c r="D9" t="n">
-        <v>28.5514</v>
+        <v>4.2058</v>
       </c>
       <c r="E9" t="n">
-        <v>4.7474</v>
+        <v>0.7469</v>
       </c>
       <c r="F9" t="n">
-        <v>4.0521</v>
+        <v>3.6689</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>5.3973e-05</t>
+          <t>2.5412e-04</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>kvp_z</t>
+          <t>Model_Alexion</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.7855</v>
+        <v>27.1589</v>
       </c>
       <c r="C10" t="n">
-        <v>1.3091</v>
+        <v>-21.3491</v>
       </c>
       <c r="D10" t="n">
-        <v>4.2619</v>
+        <v>75.66679999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7524999999999999</v>
+        <v>24.7248</v>
       </c>
       <c r="F10" t="n">
-        <v>3.7015</v>
+        <v>1.0984</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2.2392e-04</t>
+          <t>2.7223e-01</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Model_Alexion</t>
+          <t>Model_Aquilion</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>27.7225</v>
+        <v>12.734</v>
       </c>
       <c r="C11" t="n">
-        <v>-21.1403</v>
+        <v>-28.4681</v>
       </c>
       <c r="D11" t="n">
-        <v>76.5853</v>
+        <v>53.936</v>
       </c>
       <c r="E11" t="n">
-        <v>24.9056</v>
+        <v>21.0009</v>
       </c>
       <c r="F11" t="n">
-        <v>1.1131</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2.6589e-01</t>
+          <t>5.4439e-01</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Model_Aquilion</t>
+          <t>Model_Aquilion Lightning</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.6004</v>
+        <v>23.6247</v>
       </c>
       <c r="C12" t="n">
-        <v>-27.9066</v>
+        <v>-32.3589</v>
       </c>
       <c r="D12" t="n">
-        <v>55.1074</v>
+        <v>79.6083</v>
       </c>
       <c r="E12" t="n">
-        <v>21.1563</v>
+        <v>28.5352</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6429</v>
+        <v>0.8279</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>5.2044e-01</t>
+          <t>4.0788e-01</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Model_Aquilion Lightning</t>
+          <t>Model_Aquilion ONE</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>23.7615</v>
+        <v>26.8523</v>
       </c>
       <c r="C13" t="n">
-        <v>-32.6303</v>
+        <v>-14.3233</v>
       </c>
       <c r="D13" t="n">
-        <v>80.1534</v>
+        <v>68.02800000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>28.7432</v>
+        <v>20.9875</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8267</v>
+        <v>1.2794</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>4.0858e-01</t>
+          <t>2.0098e-01</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Model_Aquilion ONE</t>
+          <t>Model_Aquilion PRIME</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>27.352</v>
+        <v>14.6139</v>
       </c>
       <c r="C14" t="n">
-        <v>-14.125</v>
+        <v>-28.1276</v>
       </c>
       <c r="D14" t="n">
-        <v>68.8291</v>
+        <v>57.3554</v>
       </c>
       <c r="E14" t="n">
-        <v>21.1411</v>
+        <v>21.7856</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2938</v>
+        <v>0.6708</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.9598e-01</t>
+          <t>5.0247e-01</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Model_Aquilion PRIME</t>
+          <t>Model_Aquilion/LB</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14.4696</v>
+        <v>34.3021</v>
       </c>
       <c r="C15" t="n">
-        <v>-28.5841</v>
+        <v>-14.2888</v>
       </c>
       <c r="D15" t="n">
-        <v>57.5232</v>
+        <v>82.8929</v>
       </c>
       <c r="E15" t="n">
-        <v>21.9447</v>
+        <v>24.767</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6594</v>
+        <v>1.385</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>5.0979e-01</t>
+          <t>1.6631e-01</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Model_Aquilion/LB</t>
+          <t>Model_Brilliance 40</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>32.6502</v>
+        <v>14.3746</v>
       </c>
       <c r="C16" t="n">
-        <v>-16.3123</v>
+        <v>-41.5787</v>
       </c>
       <c r="D16" t="n">
-        <v>81.6127</v>
+        <v>70.3279</v>
       </c>
       <c r="E16" t="n">
-        <v>24.9564</v>
+        <v>28.5197</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3083</v>
+        <v>0.504</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.9102e-01</t>
+          <t>6.1434e-01</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Model_Brilliance 40</t>
+          <t>Model_Brilliance 64</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13.6493</v>
+        <v>9.414300000000001</v>
       </c>
       <c r="C17" t="n">
-        <v>-42.7144</v>
+        <v>-31.6932</v>
       </c>
       <c r="D17" t="n">
-        <v>70.0129</v>
+        <v>50.5218</v>
       </c>
       <c r="E17" t="n">
-        <v>28.7289</v>
+        <v>20.9527</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4751</v>
+        <v>0.4493</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>6.3480e-01</t>
+          <t>6.5329e-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Model_Brilliance 64</t>
+          <t>Model_Brivo CT385 Series</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>8.5192</v>
+        <v>32.9098</v>
       </c>
       <c r="C18" t="n">
-        <v>-32.8936</v>
+        <v>-15.607</v>
       </c>
       <c r="D18" t="n">
-        <v>49.932</v>
+        <v>81.4267</v>
       </c>
       <c r="E18" t="n">
-        <v>21.1083</v>
+        <v>24.7293</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4036</v>
+        <v>1.3308</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>6.8658e-01</t>
+          <t>1.8350e-01</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Model_Brivo CT385 Series</t>
+          <t>Model_Definition Edge</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>31.6906</v>
+        <v>16.074</v>
       </c>
       <c r="C19" t="n">
-        <v>-17.1892</v>
+        <v>-39.8913</v>
       </c>
       <c r="D19" t="n">
-        <v>80.57040000000001</v>
+        <v>72.0393</v>
       </c>
       <c r="E19" t="n">
-        <v>24.9143</v>
+        <v>28.5258</v>
       </c>
       <c r="F19" t="n">
-        <v>1.272</v>
+        <v>0.5635</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2.0362e-01</t>
+          <t>5.7320e-01</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Model_Definition Edge</t>
+          <t>Model_Discovery CT750 HD</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>16.6165</v>
+        <v>13.5154</v>
       </c>
       <c r="C20" t="n">
-        <v>-39.758</v>
+        <v>-26.8716</v>
       </c>
       <c r="D20" t="n">
-        <v>72.991</v>
+        <v>53.9024</v>
       </c>
       <c r="E20" t="n">
-        <v>28.7344</v>
+        <v>20.5855</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5783</v>
+        <v>0.6566</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>5.6318e-01</t>
+          <t>5.1159e-01</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Model_Discovery CT750 HD</t>
+          <t>Model_ECLOS</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>12.8146</v>
+        <v>-20.288</v>
       </c>
       <c r="C21" t="n">
-        <v>-27.8697</v>
+        <v>-76.3175</v>
       </c>
       <c r="D21" t="n">
-        <v>53.4989</v>
+        <v>35.7414</v>
       </c>
       <c r="E21" t="n">
-        <v>20.737</v>
+        <v>28.5585</v>
       </c>
       <c r="F21" t="n">
-        <v>0.618</v>
+        <v>-0.7104</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>5.3672e-01</t>
+          <t>4.7759e-01</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Model_ECLOS</t>
+          <t>Model_Emotion 16</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-20.6726</v>
+        <v>15.4587</v>
       </c>
       <c r="C22" t="n">
-        <v>-77.1129</v>
+        <v>-40.7078</v>
       </c>
       <c r="D22" t="n">
-        <v>35.7677</v>
+        <v>71.62520000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>28.7679</v>
+        <v>28.6284</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7186</v>
+        <v>0.54</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>4.7253e-01</t>
+          <t>5.8931e-01</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Model_Emotion 16</t>
+          <t>Model_Emotion 16 (2007)</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>15.645</v>
+        <v>35.7904</v>
       </c>
       <c r="C23" t="n">
-        <v>-40.9311</v>
+        <v>-20.2801</v>
       </c>
       <c r="D23" t="n">
-        <v>72.2212</v>
+        <v>91.8609</v>
       </c>
       <c r="E23" t="n">
-        <v>28.8372</v>
+        <v>28.5794</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5425</v>
+        <v>1.2523</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>5.8755e-01</t>
+          <t>2.1070e-01</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Model_Emotion 16 (2007)</t>
+          <t>Model_GMS Revolution FT</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>37.6759</v>
+        <v>75.0639</v>
       </c>
       <c r="C24" t="n">
-        <v>-18.8178</v>
+        <v>18.7241</v>
       </c>
       <c r="D24" t="n">
-        <v>94.1696</v>
+        <v>131.4037</v>
       </c>
       <c r="E24" t="n">
-        <v>28.7951</v>
+        <v>28.7167</v>
       </c>
       <c r="F24" t="n">
-        <v>1.3084</v>
+        <v>2.6139</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.9098e-01</t>
+          <t>9.0609e-03</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Model_GMS Revolution FT</t>
+          <t>Model_Ingenuity CT</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>75.3702</v>
+        <v>15.1229</v>
       </c>
       <c r="C25" t="n">
-        <v>18.6178</v>
+        <v>-27.6894</v>
       </c>
       <c r="D25" t="n">
-        <v>132.1226</v>
+        <v>57.9351</v>
       </c>
       <c r="E25" t="n">
-        <v>28.927</v>
+        <v>21.8217</v>
       </c>
       <c r="F25" t="n">
-        <v>2.6055</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>9.2852e-03</t>
+          <t>4.8843e-01</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Model_Ingenuity CT</t>
+          <t>Model_Ingenuity CT Elite</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>14.4548</v>
+        <v>-13.4882</v>
       </c>
       <c r="C26" t="n">
-        <v>-28.6726</v>
+        <v>-59.2448</v>
       </c>
       <c r="D26" t="n">
-        <v>57.5821</v>
+        <v>32.2685</v>
       </c>
       <c r="E26" t="n">
-        <v>21.9822</v>
+        <v>23.3224</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6576</v>
+        <v>-0.5783</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>5.1094e-01</t>
+          <t>5.6315e-01</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Model_Ingenuity CT Elite</t>
+          <t>Model_Ingenuity Core</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-14.7044</v>
+        <v>8.833399999999999</v>
       </c>
       <c r="C27" t="n">
-        <v>-60.804</v>
+        <v>-36.8646</v>
       </c>
       <c r="D27" t="n">
-        <v>31.3952</v>
+        <v>54.5314</v>
       </c>
       <c r="E27" t="n">
-        <v>23.4972</v>
+        <v>23.2925</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.6258</v>
+        <v>0.3792</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>5.3157e-01</t>
+          <t>7.0458e-01</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Model_Ingenuity Core</t>
+          <t>Model_Ingenuity Core 128</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>6.8462</v>
+        <v>10.3931</v>
       </c>
       <c r="C28" t="n">
-        <v>-39.2089</v>
+        <v>-31.9476</v>
       </c>
       <c r="D28" t="n">
-        <v>52.9012</v>
+        <v>52.7338</v>
       </c>
       <c r="E28" t="n">
-        <v>23.4745</v>
+        <v>21.5813</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2916</v>
+        <v>0.4816</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>7.7061e-01</t>
+          <t>6.3019e-01</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Model_Ingenuity Core 128</t>
+          <t>Model_LightSpeed VCT</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>10.3347</v>
+        <v>6.0967</v>
       </c>
       <c r="C29" t="n">
-        <v>-32.3148</v>
+        <v>-34.0003</v>
       </c>
       <c r="D29" t="n">
-        <v>52.9842</v>
+        <v>46.1938</v>
       </c>
       <c r="E29" t="n">
-        <v>21.7387</v>
+        <v>20.4377</v>
       </c>
       <c r="F29" t="n">
-        <v>0.4754</v>
+        <v>0.2983</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>6.3458e-01</t>
+          <t>7.6552e-01</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Model_LightSpeed VCT</t>
+          <t>Model_MX 16</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>5.7086</v>
+        <v>5.5278</v>
       </c>
       <c r="C30" t="n">
-        <v>-34.6817</v>
+        <v>-50.4609</v>
       </c>
       <c r="D30" t="n">
-        <v>46.0989</v>
+        <v>61.5166</v>
       </c>
       <c r="E30" t="n">
-        <v>20.5871</v>
+        <v>28.5378</v>
       </c>
       <c r="F30" t="n">
-        <v>0.2773</v>
+        <v>0.1937</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>7.8161e-01</t>
+          <t>8.4644e-01</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Model_MX 16</t>
+          <t>Model_Optima CT660</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>5.9421</v>
+        <v>14.7886</v>
       </c>
       <c r="C31" t="n">
-        <v>-50.4558</v>
+        <v>-28.4986</v>
       </c>
       <c r="D31" t="n">
-        <v>62.3399</v>
+        <v>58.0759</v>
       </c>
       <c r="E31" t="n">
-        <v>28.7463</v>
+        <v>22.0638</v>
       </c>
       <c r="F31" t="n">
-        <v>0.2067</v>
+        <v>0.6703</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>8.3627e-01</t>
+          <t>5.0281e-01</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Model_Optima CT660</t>
+          <t>Model_Revolution CT</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>14.8884</v>
+        <v>10.5018</v>
       </c>
       <c r="C32" t="n">
-        <v>-28.7145</v>
+        <v>-30.1795</v>
       </c>
       <c r="D32" t="n">
-        <v>58.4913</v>
+        <v>51.183</v>
       </c>
       <c r="E32" t="n">
-        <v>22.2246</v>
+        <v>20.7355</v>
       </c>
       <c r="F32" t="n">
-        <v>0.6699000000000001</v>
+        <v>0.5065</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>5.0305e-01</t>
+          <t>6.1262e-01</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Model_Revolution CT</t>
+          <t>Model_Revolution EVO</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>10.304</v>
+        <v>4.5817</v>
       </c>
       <c r="C33" t="n">
-        <v>-30.6745</v>
+        <v>-35.4024</v>
       </c>
       <c r="D33" t="n">
-        <v>51.2825</v>
+        <v>44.5658</v>
       </c>
       <c r="E33" t="n">
-        <v>20.8869</v>
+        <v>20.3801</v>
       </c>
       <c r="F33" t="n">
-        <v>0.4933</v>
+        <v>0.2248</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>6.2187e-01</t>
+          <t>8.2216e-01</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Model_Revolution EVO</t>
+          <t>Model_Revolution Frontier</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3.6467</v>
+        <v>-21.7765</v>
       </c>
       <c r="C34" t="n">
-        <v>-36.6294</v>
+        <v>-77.89239999999999</v>
       </c>
       <c r="D34" t="n">
-        <v>43.9228</v>
+        <v>34.3394</v>
       </c>
       <c r="E34" t="n">
-        <v>20.5289</v>
+        <v>28.6026</v>
       </c>
       <c r="F34" t="n">
-        <v>0.1776</v>
+        <v>-0.7613</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>8.5904e-01</t>
+          <t>4.4660e-01</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Model_Revolution Frontier</t>
+          <t>Model_Revolution HD</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-21.5502</v>
+        <v>10.3151</v>
       </c>
       <c r="C35" t="n">
-        <v>-78.0753</v>
+        <v>-45.6458</v>
       </c>
       <c r="D35" t="n">
-        <v>34.9749</v>
+        <v>66.2761</v>
       </c>
       <c r="E35" t="n">
-        <v>28.8111</v>
+        <v>28.5236</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.748</v>
+        <v>0.3616</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>4.5462e-01</t>
+          <t>7.1769e-01</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Model_Revolution HD</t>
+          <t>Model_SOMATOM Definition</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>9.843999999999999</v>
+        <v>17.8314</v>
       </c>
       <c r="C36" t="n">
-        <v>-46.5266</v>
+        <v>-30.7457</v>
       </c>
       <c r="D36" t="n">
-        <v>66.2145</v>
+        <v>66.4085</v>
       </c>
       <c r="E36" t="n">
-        <v>28.7324</v>
+        <v>24.76</v>
       </c>
       <c r="F36" t="n">
-        <v>0.3426</v>
+        <v>0.7202</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>7.3195e-01</t>
+          <t>4.7156e-01</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Definition</t>
+          <t>Model_SOMATOM Definition AS</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>15.0662</v>
+        <v>22.0042</v>
       </c>
       <c r="C37" t="n">
-        <v>-33.9078</v>
+        <v>-26.703</v>
       </c>
       <c r="D37" t="n">
-        <v>64.0401</v>
+        <v>70.7114</v>
       </c>
       <c r="E37" t="n">
-        <v>24.9623</v>
+        <v>24.8263</v>
       </c>
       <c r="F37" t="n">
-        <v>0.6036</v>
+        <v>0.8863</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>5.4625e-01</t>
+          <t>3.7562e-01</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Definition AS</t>
+          <t>Model_SOMATOM Definition AS+</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>24.0025</v>
+        <v>16.4427</v>
       </c>
       <c r="C38" t="n">
-        <v>-25.0842</v>
+        <v>-23.3809</v>
       </c>
       <c r="D38" t="n">
-        <v>73.0891</v>
+        <v>56.2662</v>
       </c>
       <c r="E38" t="n">
-        <v>25.0197</v>
+        <v>20.2983</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9593</v>
+        <v>0.8101</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>3.3758e-01</t>
+          <t>4.1807e-01</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Definition AS+</t>
+          <t>Model_SOMATOM Definition Edge</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>15.7292</v>
+        <v>25.008</v>
       </c>
       <c r="C39" t="n">
-        <v>-24.3891</v>
+        <v>-18.5354</v>
       </c>
       <c r="D39" t="n">
-        <v>55.8476</v>
+        <v>68.5515</v>
       </c>
       <c r="E39" t="n">
-        <v>20.4485</v>
+        <v>22.1943</v>
       </c>
       <c r="F39" t="n">
-        <v>0.7692</v>
+        <v>1.1268</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>4.4192e-01</t>
+          <t>2.6006e-01</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Definition Edge</t>
+          <t>Model_SOMATOM Definition Flash</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>23.9137</v>
+        <v>19.3581</v>
       </c>
       <c r="C40" t="n">
-        <v>-19.956</v>
+        <v>-20.4338</v>
       </c>
       <c r="D40" t="n">
-        <v>67.7835</v>
+        <v>59.15</v>
       </c>
       <c r="E40" t="n">
-        <v>22.3606</v>
+        <v>20.2822</v>
       </c>
       <c r="F40" t="n">
-        <v>1.0695</v>
+        <v>0.9544</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2.8508e-01</t>
+          <t>3.4005e-01</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Definition Flash</t>
+          <t>Model_SOMATOM Drive</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>19.4731</v>
+        <v>35.6744</v>
       </c>
       <c r="C41" t="n">
-        <v>-20.6089</v>
+        <v>-20.475</v>
       </c>
       <c r="D41" t="n">
-        <v>59.5552</v>
+        <v>91.82389999999999</v>
       </c>
       <c r="E41" t="n">
-        <v>20.43</v>
+        <v>28.6197</v>
       </c>
       <c r="F41" t="n">
-        <v>0.9532</v>
+        <v>1.2465</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>3.4070e-01</t>
+          <t>2.1282e-01</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Drive</t>
+          <t>Model_SOMATOM Emotion 16</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>36.1048</v>
+        <v>31.0071</v>
       </c>
       <c r="C42" t="n">
-        <v>-20.455</v>
+        <v>-25.0134</v>
       </c>
       <c r="D42" t="n">
-        <v>92.66459999999999</v>
+        <v>87.0275</v>
       </c>
       <c r="E42" t="n">
-        <v>28.8288</v>
+        <v>28.5539</v>
       </c>
       <c r="F42" t="n">
-        <v>1.2524</v>
+        <v>1.0859</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2.1067e-01</t>
+          <t>2.7773e-01</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Emotion 16</t>
+          <t>Model_SOMATOM Force</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>30.9695</v>
+        <v>24.0566</v>
       </c>
       <c r="C43" t="n">
-        <v>-25.4594</v>
+        <v>-15.7633</v>
       </c>
       <c r="D43" t="n">
-        <v>87.3985</v>
+        <v>63.8764</v>
       </c>
       <c r="E43" t="n">
-        <v>28.7621</v>
+        <v>20.2964</v>
       </c>
       <c r="F43" t="n">
-        <v>1.0767</v>
+        <v>1.1853</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2.8181e-01</t>
+          <t>2.3614e-01</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Force</t>
+          <t>Model_SOMATOM Perspective</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>24.4093</v>
+        <v>11.1248</v>
       </c>
       <c r="C44" t="n">
-        <v>-15.7012</v>
+        <v>-31.1701</v>
       </c>
       <c r="D44" t="n">
-        <v>64.5198</v>
+        <v>53.4196</v>
       </c>
       <c r="E44" t="n">
-        <v>20.4445</v>
+        <v>21.5579</v>
       </c>
       <c r="F44" t="n">
-        <v>1.1939</v>
+        <v>0.516</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2.3274e-01</t>
+          <t>6.0592e-01</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Perspective</t>
+          <t>Model_SOMATOM Scope</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>11.5739</v>
+        <v>12.9538</v>
       </c>
       <c r="C45" t="n">
-        <v>-31.0302</v>
+        <v>-32.7676</v>
       </c>
       <c r="D45" t="n">
-        <v>54.1779</v>
+        <v>58.6753</v>
       </c>
       <c r="E45" t="n">
-        <v>21.7155</v>
+        <v>23.3045</v>
       </c>
       <c r="F45" t="n">
-        <v>0.533</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>5.9415e-01</t>
+          <t>5.7841e-01</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Scope</t>
+          <t>Model_SOMATOM go.Top</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>12.8245</v>
+        <v>-1.8466</v>
       </c>
       <c r="C46" t="n">
-        <v>-33.2308</v>
+        <v>-58.1688</v>
       </c>
       <c r="D46" t="n">
-        <v>58.8798</v>
+        <v>54.4757</v>
       </c>
       <c r="E46" t="n">
-        <v>23.4746</v>
+        <v>28.7078</v>
       </c>
       <c r="F46" t="n">
-        <v>0.5463</v>
+        <v>-0.0643</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>5.8495e-01</t>
+          <t>9.4872e-01</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Model_SOMATOM go.Top</t>
+          <t>Model_Scope</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1.7778</v>
+        <v>20.4384</v>
       </c>
       <c r="C47" t="n">
-        <v>-55.0102</v>
+        <v>-35.5322</v>
       </c>
       <c r="D47" t="n">
-        <v>58.5659</v>
+        <v>76.40900000000001</v>
       </c>
       <c r="E47" t="n">
-        <v>28.9452</v>
+        <v>28.5285</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0614</v>
+        <v>0.7164</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>9.5103e-01</t>
+          <t>4.7387e-01</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Model_Scope</t>
+          <t>Model_Sensation 16</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>21.7606</v>
+        <v>47.6518</v>
       </c>
       <c r="C48" t="n">
-        <v>-34.6255</v>
+        <v>-8.3773</v>
       </c>
       <c r="D48" t="n">
-        <v>78.1468</v>
+        <v>103.6809</v>
       </c>
       <c r="E48" t="n">
-        <v>28.7403</v>
+        <v>28.5583</v>
       </c>
       <c r="F48" t="n">
-        <v>0.7571</v>
+        <v>1.6686</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>4.4911e-01</t>
+          <t>9.5458e-02</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Model_Sensation 16</t>
+          <t>Model_Sensation 64</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>48.598</v>
+        <v>9.9945</v>
       </c>
       <c r="C49" t="n">
-        <v>-7.8447</v>
+        <v>-29.9945</v>
       </c>
       <c r="D49" t="n">
-        <v>105.0407</v>
+        <v>49.9834</v>
       </c>
       <c r="E49" t="n">
-        <v>28.7691</v>
+        <v>20.3826</v>
       </c>
       <c r="F49" t="n">
-        <v>1.6892</v>
+        <v>0.4903</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>9.1430e-02</t>
+          <t>6.2398e-01</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Model_Sensation 64</t>
+          <t>Model_Sensation Open</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>10.5313</v>
+        <v>24.2801</v>
       </c>
       <c r="C50" t="n">
-        <v>-29.7512</v>
+        <v>-19.1436</v>
       </c>
       <c r="D50" t="n">
-        <v>50.8138</v>
+        <v>67.7038</v>
       </c>
       <c r="E50" t="n">
-        <v>20.5322</v>
+        <v>22.1333</v>
       </c>
       <c r="F50" t="n">
-        <v>0.5129</v>
+        <v>1.097</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>6.0810e-01</t>
+          <t>2.7286e-01</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Model_Sensation Open</t>
+          <t>Model_Spirit</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>26.4799</v>
+        <v>-5.2184</v>
       </c>
       <c r="C51" t="n">
-        <v>-17.2864</v>
+        <v>-61.2371</v>
       </c>
       <c r="D51" t="n">
-        <v>70.2462</v>
+        <v>50.8003</v>
       </c>
       <c r="E51" t="n">
-        <v>22.3079</v>
+        <v>28.5531</v>
       </c>
       <c r="F51" t="n">
-        <v>1.187</v>
+        <v>-0.1828</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2.3545e-01</t>
+          <t>8.5502e-01</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Model_Spirit</t>
+          <t>Model_Supria</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-3.8612</v>
+        <v>-1.1701</v>
       </c>
       <c r="C52" t="n">
-        <v>-60.2968</v>
+        <v>-57.2167</v>
       </c>
       <c r="D52" t="n">
-        <v>52.5743</v>
+        <v>54.8766</v>
       </c>
       <c r="E52" t="n">
-        <v>28.7655</v>
+        <v>28.5673</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.1342</v>
+        <v>-0.041</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>8.9324e-01</t>
+          <t>9.6734e-01</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Model_Supria</t>
+          <t>Model_iCT 256</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3.7907</v>
+        <v>13.8938</v>
       </c>
       <c r="C53" t="n">
-        <v>-52.7789</v>
+        <v>-25.7943</v>
       </c>
       <c r="D53" t="n">
-        <v>60.3602</v>
+        <v>53.5818</v>
       </c>
       <c r="E53" t="n">
-        <v>28.8338</v>
+        <v>20.2292</v>
       </c>
       <c r="F53" t="n">
-        <v>0.1315</v>
+        <v>0.6868</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>8.9543e-01</t>
+          <t>4.9233e-01</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Model_iCT 256</t>
+          <t>Model_iCT SP</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>13.6918</v>
+        <v>-29.0029</v>
       </c>
       <c r="C54" t="n">
-        <v>-26.2863</v>
+        <v>-85.01309999999999</v>
       </c>
       <c r="D54" t="n">
-        <v>53.6698</v>
+        <v>27.0074</v>
       </c>
       <c r="E54" t="n">
-        <v>20.377</v>
+        <v>28.5487</v>
       </c>
       <c r="F54" t="n">
-        <v>0.6719000000000001</v>
+        <v>-1.0159</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>5.0176e-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Model_iCT SP</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>-30.2597</v>
-      </c>
-      <c r="C55" t="n">
-        <v>-86.6854</v>
-      </c>
-      <c r="D55" t="n">
-        <v>26.1659</v>
-      </c>
-      <c r="E55" t="n">
-        <v>28.7605</v>
-      </c>
-      <c r="F55" t="n">
-        <v>-1.0521</v>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>2.9295e-01</t>
+          <t>3.0988e-01</t>
         </is>
       </c>
     </row>
@@ -3337,7 +3253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3389,10 +3305,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12.441</v>
+        <v>9.5609</v>
       </c>
       <c r="C2" t="n">
-        <v>252967.153</v>
+        <v>14198.034</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
@@ -3411,10 +3327,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1283</v>
+        <v>0.1491</v>
       </c>
       <c r="C3" t="n">
-        <v>1.1369</v>
+        <v>1.1608</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -3433,10 +3349,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4222</v>
+        <v>0.4265</v>
       </c>
       <c r="C4" t="n">
-        <v>1.5253</v>
+        <v>1.5318</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -3451,14 +3367,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>p25_z</t>
+          <t>mean_z</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.0181</v>
+        <v>-0.8475</v>
       </c>
       <c r="C5" t="n">
-        <v>2.768</v>
+        <v>0.4285</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -3477,10 +3393,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3118</v>
+        <v>0.1809</v>
       </c>
       <c r="C6" t="n">
-        <v>1.3659</v>
+        <v>1.1983</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -3499,10 +3415,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.1706</v>
+        <v>-0.2088</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8431999999999999</v>
+        <v>0.8116</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -3521,10 +3437,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5363</v>
+        <v>0.4875</v>
       </c>
       <c r="C8" t="n">
-        <v>1.7097</v>
+        <v>1.6282</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -3539,14 +3455,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mean_z</t>
+          <t>kvp_z</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-1.8158</v>
+        <v>-0.3188</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1627</v>
+        <v>0.727</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
@@ -3561,14 +3477,14 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>kvp_z</t>
+          <t>Model_Alexion</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.323</v>
+        <v>-53.5246</v>
       </c>
       <c r="C10" t="n">
-        <v>0.724</v>
+        <v>0</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
@@ -3583,11 +3499,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Model_Alexion</t>
+          <t>Model_Aquilion</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-158.4181</v>
+        <v>-10.4997</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -3605,11 +3521,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Model_Aquilion</t>
+          <t>Model_Aquilion Lightning</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-13.4322</v>
+        <v>-25.2249</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -3627,11 +3543,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Model_Aquilion Lightning</t>
+          <t>Model_Aquilion ONE</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-71.7381</v>
+        <v>-127.6476</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -3649,11 +3565,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Model_Aquilion ONE</t>
+          <t>Model_Aquilion PRIME</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-336.4169</v>
+        <v>-10.8468</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -3671,11 +3587,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Model_Aquilion PRIME</t>
+          <t>Model_Aquilion/LB</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-13.6908</v>
+        <v>-33.1418</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -3693,11 +3609,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Model_Aquilion/LB</t>
+          <t>Model_Brilliance 40</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-94.63809999999999</v>
+        <v>-17.2452</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -3715,14 +3631,14 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Model_Brilliance 40</t>
+          <t>Model_Brilliance 64</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-46.2393</v>
+        <v>-9.5047</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
@@ -3737,11 +3653,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Model_Brilliance 64</t>
+          <t>Model_Brivo CT385 Series</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-12.343</v>
+        <v>-47.0026</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -3759,11 +3675,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Model_Brivo CT385 Series</t>
+          <t>Model_Definition Edge</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-134.255</v>
+        <v>-25.5693</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -3781,14 +3697,14 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Model_Definition Edge</t>
+          <t>Model_Discovery CT750 HD</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-74.16330000000001</v>
+        <v>-9.7598</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
@@ -3803,14 +3719,14 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Model_Discovery CT750 HD</t>
+          <t>Model_ECLOS</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-12.6126</v>
+        <v>73.11669999999999</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>5.677545609178458e+31</v>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
@@ -3825,14 +3741,14 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Model_ECLOS</t>
+          <t>Model_Emotion 16</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>221.9781</v>
+        <v>-25.6438</v>
       </c>
       <c r="C22" t="n">
-        <v>2.534293354166796e+96</v>
+        <v>0</v>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
@@ -3847,11 +3763,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Model_Emotion 16</t>
+          <t>Model_Emotion 16 (2007)</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-72.8336</v>
+        <v>-57.7975</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -3869,11 +3785,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Model_Emotion 16 (2007)</t>
+          <t>Model_GMS Revolution FT</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-180.8605</v>
+        <v>-16.6665</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
@@ -3891,11 +3807,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Model_GMS Revolution FT</t>
+          <t>Model_Ingenuity CT</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-50.4704</v>
+        <v>-51.4185</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -3913,14 +3829,14 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Model_Ingenuity CT</t>
+          <t>Model_Ingenuity CT Elite</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-149.4784</v>
+        <v>-8.452299999999999</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>0.0002</v>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
@@ -3935,11 +3851,11 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Model_Ingenuity CT Elite</t>
+          <t>Model_Ingenuity Core</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-11.2957</v>
+        <v>-43.0859</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -3957,11 +3873,11 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Model_Ingenuity Core</t>
+          <t>Model_Ingenuity Core 128</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-117.7751</v>
+        <v>-10.8176</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -3979,11 +3895,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Model_Ingenuity Core 128</t>
+          <t>Model_LightSpeed VCT</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-13.7378</v>
+        <v>-10.1306</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -4001,11 +3917,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Model_LightSpeed VCT</t>
+          <t>Model_MX 16</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-12.9938</v>
+        <v>-15.4244</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -4023,11 +3939,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Model_MX 16</t>
+          <t>Model_Optima CT660</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-44.0222</v>
+        <v>-100.7545</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -4045,11 +3961,11 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Model_Optima CT660</t>
+          <t>Model_Revolution CT</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-276.4556</v>
+        <v>-10.3907</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
@@ -4067,14 +3983,14 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Model_Revolution CT</t>
+          <t>Model_Revolution EVO</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-13.253</v>
+        <v>-9.799200000000001</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
@@ -4089,14 +4005,14 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Model_Revolution EVO</t>
+          <t>Model_Revolution Frontier</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-12.6537</v>
+        <v>68.09139999999999</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>3.730161283343225e+29</v>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
@@ -4111,14 +4027,14 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Model_Revolution Frontier</t>
+          <t>Model_Revolution HD</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>202.6785</v>
+        <v>-29.695</v>
       </c>
       <c r="C35" t="n">
-        <v>1.052374639554208e+88</v>
+        <v>0</v>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
@@ -4133,11 +4049,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Model_Revolution HD</t>
+          <t>Model_SOMATOM Definition</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-85.0416</v>
+        <v>-34.6187</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
@@ -4155,11 +4071,11 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Definition</t>
+          <t>Model_SOMATOM Definition AS</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-91.3343</v>
+        <v>-47.8687</v>
       </c>
       <c r="C37" t="n">
         <v>0</v>
@@ -4177,11 +4093,11 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Definition AS</t>
+          <t>Model_SOMATOM Definition AS+</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-155.2099</v>
+        <v>-10.835</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -4199,11 +4115,11 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Definition AS+</t>
+          <t>Model_SOMATOM Definition Edge</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-13.668</v>
+        <v>-11.0874</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
@@ -4221,11 +4137,11 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Definition Edge</t>
+          <t>Model_SOMATOM Definition Flash</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-13.9577</v>
+        <v>-11.1375</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
@@ -4243,11 +4159,11 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Definition Flash</t>
+          <t>Model_SOMATOM Drive</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-14.0084</v>
+        <v>-41.7138</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
@@ -4265,11 +4181,11 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Drive</t>
+          <t>Model_SOMATOM Emotion 16</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-126.7924</v>
+        <v>-24.731</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
@@ -4287,11 +4203,11 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Emotion 16</t>
+          <t>Model_SOMATOM Force</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-69.9297</v>
+        <v>-11.6956</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -4309,11 +4225,11 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Force</t>
+          <t>Model_SOMATOM Perspective</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-14.5857</v>
+        <v>-10.1495</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
@@ -4331,11 +4247,11 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Perspective</t>
+          <t>Model_SOMATOM Scope</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-13.0461</v>
+        <v>-10.6919</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
@@ -4353,14 +4269,14 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Scope</t>
+          <t>Model_SOMATOM go.Top</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-13.5387</v>
+        <v>73.2457</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>6.45929345135871e+31</v>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
@@ -4375,14 +4291,14 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Model_SOMATOM go.Top</t>
+          <t>Model_Scope</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>198.4276</v>
+        <v>-37.7786</v>
       </c>
       <c r="C47" t="n">
-        <v>1.499748619441306e+86</v>
+        <v>0</v>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
@@ -4397,11 +4313,11 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Model_Scope</t>
+          <t>Model_Sensation 16</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-115.9572</v>
+        <v>-25.3968</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
@@ -4419,11 +4335,11 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Model_Sensation 16</t>
+          <t>Model_Sensation 64</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-77.2739</v>
+        <v>-10.1077</v>
       </c>
       <c r="C49" t="n">
         <v>0</v>
@@ -4441,11 +4357,11 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Model_Sensation 64</t>
+          <t>Model_Sensation Open</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-13.0521</v>
+        <v>-11.2871</v>
       </c>
       <c r="C50" t="n">
         <v>0</v>
@@ -4463,14 +4379,14 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Model_Sensation Open</t>
+          <t>Model_Spirit</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-14.3072</v>
+        <v>79.0372</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>2.115468607533052e+34</v>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
@@ -4485,14 +4401,14 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Model_Spirit</t>
+          <t>Model_Supria</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>229.4009</v>
+        <v>68.8883</v>
       </c>
       <c r="C52" t="n">
-        <v>4.241604318100294e+99</v>
+        <v>8.275780334643129e+29</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
@@ -4507,14 +4423,14 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Model_Supria</t>
+          <t>Model_iCT 256</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>175.9512</v>
+        <v>-10.8841</v>
       </c>
       <c r="C53" t="n">
-        <v>2.598043576068838e+76</v>
+        <v>0</v>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
@@ -4529,42 +4445,20 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Model_iCT 256</t>
+          <t>Model_iCT SP</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-13.748</v>
+        <v>117.5976</v>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>1.180312641627367e+51</v>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Model_iCT SP</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>362.1</v>
-      </c>
-      <c r="C55" t="n">
-        <v>1.811530948627932e+157</v>
-      </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
@@ -4613,7 +4507,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5879</v>
+        <v>0.5901</v>
       </c>
     </row>
     <row r="4">
@@ -4623,7 +4517,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5699</v>
+        <v>0.5726</v>
       </c>
     </row>
     <row r="5">
@@ -4633,7 +4527,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32.7041</v>
+        <v>33.6688</v>
       </c>
     </row>
     <row r="6">
@@ -4644,7 +4538,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3.6868e-195</t>
+          <t>2.5855e-197</t>
         </is>
       </c>
     </row>
@@ -4655,7 +4549,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19.8599</v>
+        <v>19.7243</v>
       </c>
     </row>
     <row r="8">
@@ -4665,7 +4559,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14.6475</v>
+        <v>14.5889</v>
       </c>
     </row>
     <row r="9">
@@ -4675,7 +4569,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11294.59</v>
+        <v>11275.2</v>
       </c>
     </row>
     <row r="10">
@@ -4685,7 +4579,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11572.48</v>
+        <v>11547.94</v>
       </c>
     </row>
   </sheetData>
@@ -4741,7 +4635,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7285</v>
+        <v>0.7282</v>
       </c>
     </row>
     <row r="5">
@@ -4751,7 +4645,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6975</v>
+        <v>0.6986</v>
       </c>
     </row>
     <row r="6">
@@ -4761,7 +4655,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7592</v>
+        <v>0.7591</v>
       </c>
     </row>
     <row r="7">
@@ -4771,7 +4665,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.8703</v>
+        <v>11.2311</v>
       </c>
     </row>
     <row r="8">
@@ -4782,7 +4676,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4.4624e-01</t>
+          <t>1.8895e-01</t>
         </is>
       </c>
     </row>
@@ -4805,7 +4699,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1811</v>
+        <v>0.1791</v>
       </c>
     </row>
     <row r="11">
@@ -4815,7 +4709,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1625</v>
+        <v>0.1623</v>
       </c>
     </row>
     <row r="12">
@@ -4825,7 +4719,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1369.13</v>
+        <v>1369.12</v>
       </c>
     </row>
     <row r="13">
@@ -4835,7 +4729,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1647.01</v>
+        <v>1641.86</v>
       </c>
     </row>
     <row r="14">
@@ -4859,7 +4753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4906,19 +4800,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>126.2088</v>
+        <v>126.2482</v>
       </c>
       <c r="C2" t="n">
-        <v>124.5655</v>
+        <v>124.6122</v>
       </c>
       <c r="D2" t="n">
-        <v>127.8522</v>
+        <v>127.8842</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8377</v>
+        <v>0.8339</v>
       </c>
       <c r="F2" t="n">
-        <v>150.6689</v>
+        <v>151.3945</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -4929,27 +4823,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>p25_z</t>
+          <t>mean_z</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.3537</v>
+        <v>6.6509</v>
       </c>
       <c r="C3" t="n">
-        <v>-9.017099999999999</v>
+        <v>4.9254</v>
       </c>
       <c r="D3" t="n">
-        <v>17.7246</v>
+        <v>8.3765</v>
       </c>
       <c r="E3" t="n">
-        <v>6.8154</v>
+        <v>0.8796</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6388</v>
+        <v>7.5617</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>5.2307e-01</t>
+          <t>7.6189e-14</t>
         </is>
       </c>
     </row>
@@ -4960,23 +4854,23 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-3.6167</v>
+        <v>-4.2724</v>
       </c>
       <c r="C4" t="n">
-        <v>-6.2534</v>
+        <v>-6.0599</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.9799</v>
+        <v>-2.4849</v>
       </c>
       <c r="E4" t="n">
-        <v>1.344</v>
+        <v>0.9111</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.6909</v>
+        <v>-4.6891</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>7.2190e-03</t>
+          <t>3.0422e-06</t>
         </is>
       </c>
     </row>
@@ -4987,23 +4881,23 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.846</v>
+        <v>1.6622</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-0.1329</v>
       </c>
       <c r="D5" t="n">
-        <v>3.763</v>
+        <v>3.4573</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9772</v>
+        <v>0.915</v>
       </c>
       <c r="F5" t="n">
-        <v>1.8891</v>
+        <v>1.8166</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>5.9101e-02</t>
+          <t>6.9514e-02</t>
         </is>
       </c>
     </row>
@@ -5014,50 +4908,23 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.6175</v>
+        <v>2.5592</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8945</v>
+        <v>0.8518</v>
       </c>
       <c r="D6" t="n">
-        <v>4.3404</v>
+        <v>4.2665</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8782</v>
+        <v>0.8703</v>
       </c>
       <c r="F6" t="n">
-        <v>2.9804</v>
+        <v>2.9406</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2.9335e-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>mean_z</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2.5296</v>
-      </c>
-      <c r="C7" t="n">
-        <v>-10.3473</v>
-      </c>
-      <c r="D7" t="n">
-        <v>15.4065</v>
-      </c>
-      <c r="E7" t="n">
-        <v>6.5637</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.3854</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>7.0001e-01</t>
+          <t>3.3354e-03</t>
         </is>
       </c>
     </row>
@@ -5072,7 +4939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5124,56 +4991,56 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-1.1381</v>
+        <v>-1.1372</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3204</v>
+        <v>0.3207</v>
       </c>
       <c r="D2" t="n">
-        <v>0.281</v>
+        <v>0.2813</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3654</v>
+        <v>0.3657</v>
       </c>
       <c r="F2" t="n">
-        <v>0.06710000000000001</v>
+        <v>0.067</v>
       </c>
       <c r="G2" t="n">
-        <v>-16.9738</v>
+        <v>-16.974</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1.2834e-64</t>
+          <t>1.2787e-64</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>p25_z</t>
+          <t>mean_z</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9167999999999999</v>
+        <v>-0.3696</v>
       </c>
       <c r="C3" t="n">
-        <v>2.5014</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7496</v>
+        <v>0.5915</v>
       </c>
       <c r="E3" t="n">
-        <v>8.347</v>
+        <v>0.8073</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6148</v>
+        <v>0.0794</v>
       </c>
       <c r="G3" t="n">
-        <v>1.4912</v>
+        <v>-4.6563</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.3591e-01</t>
+          <t>3.2198e-06</t>
         </is>
       </c>
     </row>
@@ -5184,26 +5051,26 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2589</v>
+        <v>0.1374</v>
       </c>
       <c r="C4" t="n">
-        <v>1.2955</v>
+        <v>1.1473</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0505</v>
+        <v>0.9968</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5976</v>
+        <v>1.3206</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1069</v>
+        <v>0.0718</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4209</v>
+        <v>1.9149</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.5484e-02</t>
+          <t>5.5502e-02</t>
         </is>
       </c>
     </row>
@@ -5214,26 +5081,26 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.1503</v>
+        <v>-0.196</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8605</v>
+        <v>0.822</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7386</v>
+        <v>0.7131999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0024</v>
+        <v>0.9475</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0779</v>
+        <v>0.0725</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.929</v>
+        <v>-2.7041</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5.3736e-02</t>
+          <t>6.8493e-03</t>
         </is>
       </c>
     </row>
@@ -5244,56 +5111,26 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.0275</v>
+        <v>-0.0389</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9729</v>
+        <v>0.9619</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8244</v>
+        <v>0.8134</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1481</v>
+        <v>1.1375</v>
       </c>
       <c r="F6" t="n">
-        <v>0.08450000000000001</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3254</v>
+        <v>-0.4543</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>7.4489e-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>mean_z</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>-1.2321</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.2917</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.0922</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.9225</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.5875</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-2.0973</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>3.5969e-02</t>
+          <t>6.4960e-01</t>
         </is>
       </c>
     </row>
@@ -5340,7 +5177,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0741</v>
+        <v>0.074</v>
       </c>
     </row>
     <row r="4">
@@ -5350,7 +5187,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0704</v>
+        <v>0.07099999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -5360,7 +5197,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.2034</v>
+        <v>25.2424</v>
       </c>
     </row>
     <row r="6">
@@ -5371,7 +5208,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.9629e-19</t>
+          <t>3.8498e-20</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5219,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>29.7692</v>
+        <v>29.6475</v>
       </c>
     </row>
     <row r="8">
@@ -5392,7 +5229,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24.0924</v>
+        <v>24.0766</v>
       </c>
     </row>
     <row r="9">
@@ -5402,7 +5239,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12225.91</v>
+        <v>12213.51</v>
       </c>
     </row>
     <row r="10">
@@ -5412,7 +5249,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12256.78</v>
+        <v>12239.24</v>
       </c>
     </row>
   </sheetData>
@@ -5468,7 +5305,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.609</v>
+        <v>0.6117</v>
       </c>
     </row>
     <row r="5">
@@ -5478,7 +5315,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.575</v>
+        <v>0.5770999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -5488,7 +5325,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6429</v>
+        <v>0.647</v>
       </c>
     </row>
     <row r="7">
@@ -5498,7 +5335,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11.8752</v>
+        <v>9.1518</v>
       </c>
     </row>
     <row r="8">
@@ -5509,7 +5346,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.5686e-01</t>
+          <t>3.2965e-01</t>
         </is>
       </c>
     </row>
@@ -5532,7 +5369,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0394</v>
+        <v>0.0369</v>
       </c>
     </row>
     <row r="11">
@@ -5542,7 +5379,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1826</v>
+        <v>0.1825</v>
       </c>
     </row>
     <row r="12">
@@ -5552,7 +5389,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1404.41</v>
+        <v>1404.66</v>
       </c>
     </row>
     <row r="13">
@@ -5562,7 +5399,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1435.28</v>
+        <v>1430.39</v>
       </c>
     </row>
     <row r="14">
@@ -5633,19 +5470,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>103.9773</v>
+        <v>103.9813</v>
       </c>
       <c r="C2" t="n">
-        <v>102.2904</v>
+        <v>102.3112</v>
       </c>
       <c r="D2" t="n">
-        <v>105.6642</v>
+        <v>105.6514</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8599</v>
+        <v>0.8512999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>120.9237</v>
+        <v>122.1455</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -5660,23 +5497,23 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>44.2886</v>
+        <v>44.3591</v>
       </c>
       <c r="C3" t="n">
-        <v>41.9035</v>
+        <v>41.9978</v>
       </c>
       <c r="D3" t="n">
-        <v>46.6737</v>
+        <v>46.7204</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2157</v>
+        <v>1.2036</v>
       </c>
       <c r="F3" t="n">
-        <v>36.4297</v>
+        <v>36.855</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2.4330e-199</t>
+          <t>1.2575e-202</t>
         </is>
       </c>
     </row>
@@ -5687,23 +5524,23 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-4.1988</v>
+        <v>-4.1507</v>
       </c>
       <c r="C4" t="n">
-        <v>-5.3913</v>
+        <v>-5.3314</v>
       </c>
       <c r="D4" t="n">
-        <v>-3.0063</v>
+        <v>-2.9701</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6079</v>
+        <v>0.6018</v>
       </c>
       <c r="F4" t="n">
-        <v>-6.9075</v>
+        <v>-6.8972</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>7.7908e-12</t>
+          <t>8.3553e-12</t>
         </is>
       </c>
     </row>
@@ -5896,7 +5733,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5145999999999999</v>
+        <v>0.5203</v>
       </c>
     </row>
     <row r="4">
@@ -5906,7 +5743,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5139</v>
+        <v>0.5195</v>
       </c>
     </row>
     <row r="5">
@@ -5916,7 +5753,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>671.1435</v>
+        <v>686.5484</v>
       </c>
     </row>
     <row r="6">
@@ -5927,7 +5764,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.9390e-199</t>
+          <t>1.1463e-202</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5775,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21.5534</v>
+        <v>21.3386</v>
       </c>
     </row>
     <row r="8">
@@ -5948,7 +5785,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15.9728</v>
+        <v>15.9332</v>
       </c>
     </row>
     <row r="9">
@@ -5958,7 +5795,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11400.28</v>
+        <v>11374.86</v>
       </c>
     </row>
     <row r="10">
@@ -5968,7 +5805,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11415.72</v>
+        <v>11390.3</v>
       </c>
     </row>
   </sheetData>
@@ -6024,7 +5861,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6105</v>
+        <v>0.6097</v>
       </c>
     </row>
     <row r="5">
@@ -6034,7 +5871,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5748</v>
+        <v>0.5684</v>
       </c>
     </row>
     <row r="6">
@@ -6044,7 +5881,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.651</v>
+        <v>0.6476</v>
       </c>
     </row>
     <row r="7">
